--- a/public/templates/BG_Prime_Inc_statement.xlsx
+++ b/public/templates/BG_Prime_Inc_statement.xlsx
@@ -132,7 +132,7 @@
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$$]#,##0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -157,6 +157,11 @@
       <name val="Calibri"/>
     </font>
     <font/>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -407,7 +412,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="58">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -549,6 +554,12 @@
     </xf>
     <xf borderId="6" fillId="3" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="18" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1401,35 +1412,35 @@
       <c r="J49" s="51"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="23" t="s">
+      <c r="A50" s="52"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="52"/>
+      <c r="G50" s="52"/>
+      <c r="H50" s="52"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="54"/>
+      <c r="K50" s="55"/>
+      <c r="L50" s="55"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="7"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="J50" s="26">
-        <f>SUM(J49)</f>
+      <c r="J51" s="26">
+        <f>SUM(J48:J50)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="27"/>
-      <c r="B51" s="27"/>
-      <c r="C51" s="27"/>
-      <c r="D51" s="27"/>
-      <c r="E51" s="27"/>
-      <c r="F51" s="27"/>
-      <c r="G51" s="27"/>
-      <c r="H51" s="27"/>
-      <c r="I51" s="27"/>
-      <c r="J51" s="27"/>
-      <c r="K51" s="22"/>
-      <c r="L51" s="22"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="27"/>
@@ -1455,7 +1466,7 @@
       <c r="G53" s="27"/>
       <c r="H53" s="27"/>
       <c r="I53" s="27"/>
-      <c r="J53" s="22"/>
+      <c r="J53" s="27"/>
       <c r="K53" s="22"/>
       <c r="L53" s="22"/>
     </row>
@@ -1469,7 +1480,7 @@
       <c r="G54" s="27"/>
       <c r="H54" s="27"/>
       <c r="I54" s="27"/>
-      <c r="J54" s="27"/>
+      <c r="J54" s="22"/>
       <c r="K54" s="22"/>
       <c r="L54" s="22"/>
     </row>
@@ -1488,44 +1499,58 @@
       <c r="L55" s="22"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="7"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="52" t="s">
+      <c r="A56" s="27"/>
+      <c r="B56" s="27"/>
+      <c r="C56" s="27"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="27"/>
+      <c r="I56" s="27"/>
+      <c r="J56" s="27"/>
+      <c r="K56" s="22"/>
+      <c r="L56" s="22"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="7"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
+      <c r="J57" s="56" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="27"/>
-      <c r="B57" s="27"/>
-      <c r="C57" s="27"/>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
-      <c r="H57" s="27"/>
-      <c r="I57" s="27"/>
-      <c r="J57" s="53">
-        <f>SUM((J20+J50)-J33-J45)</f>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="27"/>
+      <c r="B58" s="27"/>
+      <c r="C58" s="27"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="27"/>
+      <c r="I58" s="27"/>
+      <c r="J58" s="57">
+        <f>SUM((J20+J51)-J33-J45)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="C59" s="7"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="C60" s="7"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="B30:H30"/>
+    <mergeCell ref="B31:H31"/>
     <mergeCell ref="B32:H32"/>
-    <mergeCell ref="B31:H31"/>
     <mergeCell ref="B24:H24"/>
     <mergeCell ref="B25:H25"/>
     <mergeCell ref="B26:H26"/>
